--- a/important_mails_2026-05-14.xlsx
+++ b/important_mails_2026-05-14.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1015,7 +1015,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>付款/资金类</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1030,73 +1030,21 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Thu, 7 May 2026 18:10:42 +0000</t>
+          <t>Wed, 13 May 2026 14:53:51 +0000</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+          <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Your FBA request is complete (toabAY9R4I)</t>
+          <t>Download your China tax report for October - December 2025</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral-europe.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-6481250-1667106
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
-------------------------------------------------------------------------------
-Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
-and EU wide.
-------------------------------------------------------------------------------
-Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-EUAmazon-1266639044756489</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 13 May 2026 14:53:51 +0000</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Download your China tax report for October - December 2025</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -1113,40 +1061,40 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:51 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -1161,40 +1109,40 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:28 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -1208,40 +1156,40 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:15:37 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0G6XCTGJC, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -1255,41 +1203,41 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:37:14 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Votre facture pour les frais de paiement au titre de la REP pour
  les ventes sur Amazon.fr |   Your VAT invoice for EPR Pay on Behalf charges
  for Amazon.fr sales</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Votre facture pour couvrant les frais de paiement au titre de la Responsabilité élargie du producteur (REP) pour les ventes sur Amazon.fr est désormais disponible.
@@ -1300,39 +1248,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Wed, 13 May 2026 16:40:18 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -1360,39 +1308,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Wed, 13 May 2026 14:51:48 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Zespół Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Pobierz raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Możesz teraz pobrać kwartalny raport podatkowy, który zawiera dane, takie jak informacje identyfikacyjne, liczba transakcji, przychody oraz prowizje i opłaty za usługi.
@@ -1408,39 +1356,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Tue, 12 May 2026 10:10:51 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>EPR Pay on Behalf charges for 2024 Amazon.co.uk sales</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -1459,39 +1407,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 12:21:34 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -1513,39 +1461,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Sun, 10 May 2026 16:22:50 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -1567,39 +1515,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 16:23:48 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 4/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -1618,39 +1566,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 08:34:05 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1662,39 +1610,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 07:22:14 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1706,39 +1654,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 07:02:56 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 4/2026</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Credit Note for the month of 4/2026 is now available in your Seller Central Account.
@@ -1750,39 +1698,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:29:17 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1794,39 +1742,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:25:39 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -1838,39 +1786,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:10:57 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1882,39 +1830,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:09:44 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 4/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -1933,39 +1881,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:01:18 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 4/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -1984,39 +1932,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:25:07 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Realizacja przez Amazon za 4 2026</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Realizacja przez Amazon za miesiąc 4 i rok 2026.
@@ -2028,39 +1976,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:24:35 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -2072,39 +2020,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:03:04 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -2116,39 +2064,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 20:51:50 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -2160,39 +2108,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:44:14 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Sprzedawcy za 4 2026</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Sprzedawcy za miesiąc 4 i rok 2026.
@@ -2204,39 +2152,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:35:59 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -2248,39 +2196,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:24:07 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -2292,39 +2240,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:18:06 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -2336,39 +2284,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 16:33:15 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -2380,39 +2328,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 16:20:52 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -2424,39 +2372,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 15:43:38 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -2468,39 +2416,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 15:17:48 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -2512,39 +2460,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 14:52:53 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -2556,40 +2504,40 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 14:40:42 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 4/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -2608,39 +2556,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:57:28 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -2652,39 +2600,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:43:13 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -2696,39 +2644,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:40:52 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -2740,39 +2688,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:55:06 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -2784,39 +2732,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:49:29 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -2828,39 +2776,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:20:15 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -2881,39 +2829,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 04:43:42 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-21</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -2937,39 +2885,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 03:34:49 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -2992,44 +2940,96 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 11:38:29 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>You have until July 11 to verify FBA dimensions for fee calculation</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">As previously communicated, we've updated the way we collect Fulfilment by Amazon (FBA) item package dimensions for products listed in our UK, Germany, France, Italy and Spain stores.
  96
  As previously communicated, we've updated the way we collect Fulfilment by Amazon (FBA) item package dimensions for products listed in our UK, Germany, France, Italy and Spain stores.
                                                      ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ </t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 7 May 2026 18:10:42 +0000</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (toabAY9R4I)</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed your destroy request.
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral-europe.amazon.com/
+For a complete list of inventory being destroyed, go to:
+https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-6481250-1667106
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+------------------------------------------------------------------------------
+Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
+and EU wide.
+------------------------------------------------------------------------------
+Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-EUAmazon-1266639044756489</t>
         </is>
       </c>
     </row>
@@ -3393,7 +3393,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>付款/资金类</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3408,73 +3408,21 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 04:59:05 +0000</t>
+          <t>Thu, 7 May 2026 15:03:42 +0000</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Your FBA request is complete (26041219YV)</t>
+          <t>Tu pago está en camino</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral-europe.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-2198715-0729366
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
-------------------------------------------------------------------------------
-Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
-and EU wide.
-------------------------------------------------------------------------------
-Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-EUAmazon-1917549922685067</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 7 May 2026 15:03:42 +0000</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>Tu pago está en camino</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3491,39 +3439,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:28 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3543,39 +3491,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:01:21 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3595,39 +3543,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 03:44:19 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3644,39 +3592,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 15:00:39 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 87.72 in an attempt to settle your account balance.
@@ -3691,39 +3639,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 14:45:41 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -3739,39 +3687,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 15:23:38 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>欧洲亚马逊 Payments &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>跨账户负余额调整</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3791,39 +3739,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 23:31:40 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3843,39 +3791,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:27:01 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3892,39 +3840,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:26:48 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3944,39 +3892,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 17:03:06 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3996,39 +3944,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:56 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4045,39 +3993,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:50 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4097,39 +4045,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Apr 2026 05:12:21 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;seller-notification@amazon.ie&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Outstanding balance on your Amazon account</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>Hello,
  You have an outstanding balance on your account in the amount of 7,79 EUR. We will debit this amount from the credit card (Visa) that you registered as the charge method for your account.
@@ -4143,39 +4091,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 15:01:26 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4195,39 +4143,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 14:27:43 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4244,39 +4192,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:45:45 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -4292,39 +4240,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:44:32 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4344,39 +4292,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:38:30 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4393,83 +4341,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 13 Apr 2026 16:26:54 +0000</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Payments Europe &lt;amazon_te@amazon.fr&gt;</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>Paiement du solde de votre compte de paiement Vendre sur Amazon</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>Cher vendeur,
- Nous avons débité votre carte bancaire (Visa) pour un montant de 242,36 EUR pour le règlement du solde de votre compte de paiement Vendre sur Amazon.
- Le montant débité sur votre carte bancaire peut être inférieur au montant total impayé si vous disposez d'une limite de crédit imposée par votre banque. Nous continuerons d'essayer de débiter votre carte bancaire toutes les 24 heures jusqu'à ce que le solde restant de votre compte soit entièrement payé.
- Vous pouvez également utiliser la fonction Effectuer un paiement pour régler le solde. Pour en savoir plus, recherchez « Effectuer un paiement » dans l'Aide de Seller Central.
- Vous pouvez consulter votre solde à tout moment en vous connectant à la section Rapport sur les paiements de votre compte.
- Merci de vendre sur Amazon.
-Amazon Payments Europe SCA (société en commandite par actions) est immatriculée au Registre de Commerce et des Sociétés de Luxembourg (n° 153 265) et sise 38, avenue John F. Kennedy, L-1855 Luxembourg. Numéro de TVA : LU 24448288. Amazon Payments Europe SCA est autorisée par la Commission de Surveillance du Secteur Financier en tant qu’établissement de monnaie électronique (licence n° 36/10). Ama</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 17:50:39 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -4488,39 +4392,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 12:49:24 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -4544,39 +4448,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 02:13:07 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4594,39 +4498,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 13:18:47 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4644,39 +4548,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 13:15:01 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4694,39 +4598,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:13:49 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4744,39 +4648,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:19:29 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4794,39 +4698,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 12:52:07 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -4842,39 +4746,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:11:27 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4892,39 +4796,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:14:16 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4942,39 +4846,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 13:03:36 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -4984,39 +4888,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 09:05:17 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>【请勿回复此日志，如有问题请加入下方邮件中的企微群】
 卖家您好，
@@ -5037,39 +4941,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:13:11 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -5085,39 +4989,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:52:19 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -5136,39 +5040,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 03:13:33 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20093870001] Other account issues</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Hello from Amazon Selling Partner Support,
 My name is Ritam. I am a Live Channel Specialist and I'm contacting you to follow up on your concern regarding the reinstatement of your listing B0FCDRNTT8.
@@ -5179,39 +5083,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Apr 2026 17:15:23 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -5230,39 +5134,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:15:37 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -5281,39 +5185,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:09:18 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -5332,39 +5236,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 03:03:00 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -5384,39 +5288,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 01:27:00 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20061337331] 对危险品分类提出异议</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商:您好!
 我们了解到您希望重新激活商品 ASIN: B0FCDRNTT8。
@@ -5445,39 +5349,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 10:07:05 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -5495,39 +5399,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:15:48 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5545,39 +5449,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:08:57 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5595,39 +5499,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 06:10:23 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>"compliance-ops-mass-programs@amazon.com" &lt;compliance-ops-mass-programs@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12449434352] 【邀请函】诚邀您参与亚马逊卖家合规策略调研</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴，
 您好！
@@ -5641,39 +5545,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 21:09:24 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5691,40 +5595,40 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 14:16:35 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -5741,40 +5645,40 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 09:57:17 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -5791,39 +5695,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 16:06:35 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>苏浩然 &lt;suhr@cvc.org.cn&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Amazon DV TIC</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，您好。
 我们可以为您提供亚马逊DV验证报告服务。
@@ -5857,39 +5761,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 10:14:18 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -5904,39 +5808,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 03:38:27 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -5952,39 +5856,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 11:22:53 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您在【欧洲】站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】或【已通过】。
@@ -6008,39 +5912,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 17:53:23 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -6059,183 +5963,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 09:10:03 +0000</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon-Fulfilled Inventory - Action Required</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>Dear Seller,
-You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
-Please create a removal request for the ASIN(s) listed below to have your inventory sent to a location of your choice. If this inventory is not removed within 30 days of this notification (by 10/05/2026), we shall dispose of it in accordance with our FBA policies.
-For more information regarding the removal of this product, see the notification e-mail you received from our Seller Performance Team.
-Thank you for your prompt attention to this matter.
-Yours faithfully,
-Fulfilment by Amazon Team
-Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
-Affected Product(s):
-B0GKPTF1T7
- SPC-EUAmazon-510175039347142</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 07:35:31 +0000</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>Seller Assistant now available in the UK</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>Seller Assistant now available in the UK
-[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EMUSSMX-PD25/7z2r9lq/6605548725/h/3xRPn8Yyq31Jz0Gqi8FK51O58vBJkaDT5nhLB1ousbA)
-Dear Seller,
-Managing your business on Amazon just got easier.
-[Seller Assistant](https://go.amazonsellerservices.com/e/229492/nter-assistant-ld-EMUSSMX-PD25/7z2r9lt/6605548725/h/3xRPn8Yyq31Jz0Gqi8FK51O58vBJkaDT5nhLB1ousbA) is now available in the UK within Seller Central. This AI-powered assistant helps you find relevant information, access insights, and manage your business more efficiently, directly where you already work.
-[Seller Assistant](https://go.amazonsellerservices.com/e/229492/nter-assistant-ld-EMUSSMX-PD25/7z2r9lt/6605548725/h/3xRPn8Yyq31Jz0Gqi8FK51O58vBJkaDT5nhLB1ousbA) provides guidance on our tools, policies, and processes using information available across Seller Central, along with personalized responses based on your account data. This allows you to quickly surface insights related to your business performance, inventory planning, listing, compliance, and account health without navigating multiple pages.
-[Seller Assistant](https://go.amazonsellerservices.com/e/229492/nter-assistant-l</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 06:23:28 +0000</t>
-        </is>
-      </c>
-      <c r="E117" s="2" t="inlineStr">
-        <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.com Inventory</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t>Dear Weihai US,
-You recently received a notice about the removal of your listing(s) for the product(s) listed below.
-You were required to submit a removal request for the ASIN(s) referenced below to have your inventory sent to a location of your choosing within 30 days of the notification sent on 03/13/2026. Since a removal order was not submitted since the notification was sent, we have submitted a disposal order for this inventory in accordance with FBA policies.
-For more information regarding the restriction of this product, see the notification e-mail you received from Product Safety. If you have additional questions, please contact Seller Support.
-Thank you for your attention to this matter.
-Regards,
-Product Safety Team
-Amazon.com
-www.amazon.com
-Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
-Affected Product(s):
-B0FCDRNTT8
-Was this email helpful?
- https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=RESTRICTED_PRODUCT_REMOVAL_ORDER_CREATED
-SPC-USAmazon-862019321040611</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 15:00:42 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6250,39 +6010,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 14:24:59 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Merchant Invoice for 4/2026 (Amazon.ae فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 4/2026)</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -6301,39 +6061,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 05:32:15 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -6355,39 +6115,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 15:27:47 +0600</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Amazon Review Deals &lt;amazonreviewsdeals1@gmail.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Amazon Review Rating Deals</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>Not getting sales on Amazon? Even after doing everything right? Then this
 message is for you!
@@ -6413,40 +6173,40 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 03:15:52 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -6462,40 +6222,40 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:15:51 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -6511,39 +6271,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:15:45 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -6559,39 +6319,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 01:23:15 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -6607,39 +6367,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 15:09:15 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -6655,39 +6415,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:16:19 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -6701,39 +6461,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:33:13 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 04/2026</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -6751,40 +6511,40 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:13:34 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -6800,39 +6560,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:13:30 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -6848,39 +6608,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 01:21:43 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -6896,40 +6656,40 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 01:18:50 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -6945,39 +6705,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 21:55:17 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>规划您的 La French Week 促销活动</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -6994,39 +6754,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 21:32:46 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -7055,39 +6815,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 15:08:42 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -7103,39 +6863,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:12:49 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -7149,39 +6909,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:07:32 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -7196,39 +6956,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 10:18:53 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -7248,39 +7008,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 20:59:56 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para mayo</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para mayo
@@ -7309,40 +7069,40 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:37:52 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Il team di Gestione multicanale &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Aggiornamenti ai costi di Gestione multicanale in vigore dal 29
  maggio 2026</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
  Stiamo aggiornando le tariffe di Gestione multicanale per aiutarti a ridurre i costi e investire nella crescita della tua attività.
@@ -7355,39 +7115,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:30:37 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>The Multichannel Fulfillment team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>MCF fee updates effective May 29, 2026</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  We’re updating our Multichannel Fulfillment fees to help you reduce your costs so you can invest in growing your business.
@@ -7402,39 +7162,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:25:56 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>El Departamento de Logística Multicanal &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Actualización de las tarifas de Logística Multicanal en vigor a partir del 29 de mayo de 2026</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
  Vamos a actualizar nuestras tarifas de Logística Multicanal para ayudarte a reducir los costes y así puedas invertir en hacer crecer tu negocio.
@@ -7447,40 +7207,40 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:38:42 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Presenta documentos de cumplimiento normativo del producto para
  evitar que se retiren los listings</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta documentos de cumplimiento normativo del producto para evitar que se retiren los listings
@@ -7495,40 +7255,40 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:25:34 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Documenten over productconformiteit indienen om verwijdering van
  productvermeldingen te voorkomen</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
  Documenten over productconformiteit indienen om verwijdering van productvermeldingen te voorkomen
@@ -7542,39 +7302,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:06:50 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty
@@ -7588,39 +7348,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:58:32 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort
@@ -7635,39 +7395,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:54:06 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte
@@ -7681,39 +7441,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:50:08 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente
@@ -7728,39 +7488,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 15:58:40 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -7775,39 +7535,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Mon, 27 Apr 2026 05:22:10 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -7826,39 +7586,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 11:10:42 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -7874,39 +7634,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 05:38:32 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -7927,39 +7687,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:19:11 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -7977,40 +7737,40 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:18:24 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -8028,39 +7788,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:15:32 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -8077,39 +7837,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:50 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -8127,40 +7887,40 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:30 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -8178,39 +7938,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:09:22 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -8228,39 +7988,39 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 00:31:36 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>规划您的 La French Week 促销活动</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -8277,39 +8037,39 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8324,39 +8084,39 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 07:42:42 +0000</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8375,39 +8135,39 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:32:20 +0000</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Prime Day：立即提报您的促销</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>Prime Day（日期待公布）：立即提报您的促销
 尊敬的卖家，
@@ -8425,39 +8185,39 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:19:47 +0000</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以重新启售商品</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品安全文件以重新启售商品
@@ -8496,39 +8256,39 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:17:42 +0000</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -8544,40 +8304,40 @@
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:17:14 +0000</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -8593,39 +8353,39 @@
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:13:36 +0000</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -8641,39 +8401,39 @@
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:13:34 +0000</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -8687,40 +8447,40 @@
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:11:30 +0000</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -8736,39 +8496,39 @@
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:09:39 +0000</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -8784,39 +8544,39 @@
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 05:22:42 +0000</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -8837,39 +8597,39 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 15:14:51 +0000</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -8884,39 +8644,39 @@
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 09:39:52 +0000</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Verify your primary operating address for tax purposes</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  Verify your primary operating address for tax purposes
@@ -8933,39 +8693,39 @@
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:10:49 +0000</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>[Formal Notice – Immediate Action Required] Review and certify your business information within 10 days to avoid account deactivation</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -8979,39 +8739,39 @@
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:59:02 +0000</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>Amazon Verkaeuferservice &lt;merch.service05@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12354633592] 其他账户问题</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴：
 您好！
@@ -9030,40 +8790,40 @@
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:22:14 +0000</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>Amazon Product Support Team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>Reduce Returns &amp; Boost Customer Satisfaction - Enrol in Amazon
  Product Support</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr"/>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>96
  Enrol now into Amazon Product Support !
@@ -9077,39 +8837,39 @@
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 04:46:00 +0000</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr"/>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9133,39 +8893,39 @@
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 04:25:43 +0000</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr"/>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9189,39 +8949,39 @@
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 03:35:07 +0000</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-07</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr"/>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -9242,39 +9002,39 @@
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 04:00:50 +0000</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-30</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr"/>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -9296,39 +9056,39 @@
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 03:30:46 +0000</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr"/>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9351,39 +9111,39 @@
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:58:06 +0000</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-23</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr"/>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -9404,39 +9164,39 @@
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:27:29 +0000</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr"/>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9459,39 +9219,39 @@
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 00:16:37 +0000</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr"/>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -9521,39 +9281,39 @@
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 18:05:15 +0000</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>提交商品合规文件，以避免商品被移除</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr"/>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品合规文件，以避免商品被移除
@@ -9602,39 +9362,39 @@
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 11:41:39 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>GTTC国际业务部玩具组 &lt;gttctoy@cngttc.cn&gt;</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>AMAZON DV TIC TRF ID--Top urgently</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr"/>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>Dear Vendor,        Some of your TR numbers on Amazon have been pending in our backend for a long time without timely processing. We plan to automatically clear all unresponded TR numbers in our system two days later.
 If you have any TR numbers that require sample submission for testing, please reply to this email and send us the corresponding TR numbers within two days, and contact our relevant customer service within one week to arrange sample submission.
@@ -9643,39 +9403,39 @@
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 02:18:44 +0000</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr"/>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
